--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2661E46-4984-4132-8D76-D3770046052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,8 +54,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +73,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -93,11 +107,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -403,16 +423,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="3" width="8.90625" customWidth="1"/>
-    <col min="4" max="5" width="12.90625" customWidth="1"/>
-    <col min="6" max="7" width="8.90625" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" customWidth="1"/>
-    <col min="9" max="9" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="5" width="12.88671875" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -443,6 +463,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H2" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -452,9 +475,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -463,9 +486,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2661E46-4984-4132-8D76-D3770046052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F331F4B4-AF6F-4C0D-A8B8-103863A050F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>项目名称*</t>
   </si>
   <si>
-    <t>剩余融资期限*</t>
-  </si>
-  <si>
     <t>到期收益分配*</t>
   </si>
   <si>
@@ -49,6 +46,10 @@
   </si>
   <si>
     <t>生效截止日期（yyyy-mm-dd）*</t>
+  </si>
+  <si>
+    <t>剩余融资期限（天）*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -107,7 +108,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -118,6 +119,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,12 +431,13 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" customWidth="1"/>
-    <col min="4" max="5" width="12.88671875" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" customWidth="1"/>
-    <col min="8" max="8" width="26.21875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="28.21875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -445,23 +450,23 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F331F4B4-AF6F-4C0D-A8B8-103863A050F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,20 +41,106 @@
     <t>风险状况*</t>
   </si>
   <si>
-    <t>生效日（yyyy-mm-dd）*</t>
-  </si>
-  <si>
-    <t>生效截止日期（yyyy-mm-dd）*</t>
-  </si>
-  <si>
     <t>剩余融资期限（天）*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>生效日（yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dd）*</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>生效截止日期（yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dd）*</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -112,9 +197,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -122,6 +204,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,20 +512,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,8 +535,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>8</v>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -462,15 +547,15 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H2" s="3"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -480,9 +565,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -491,9 +576,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail001.xlsx
@@ -42,7 +42,7 @@
   </si>
   <si>
     <t>剩余融资期限（天）*</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -88,7 +88,7 @@
       </rPr>
       <t>dd）*</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -134,21 +134,14 @@
       </rPr>
       <t>dd）*</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,16 +190,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -521,8 +514,8 @@
     <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -535,7 +528,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
@@ -547,18 +540,18 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="H2" s="2"/>
+      <c r="H2" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -569,7 +562,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -580,7 +573,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
